--- a/results/final_N33_v5/validation/Interpolation_Comparison.xlsx
+++ b/results/final_N33_v5/validation/Interpolation_Comparison.xlsx
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.0484</v>
+        <v>1.1101</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8646</v>
+        <v>0.9014</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0482</v>
+        <v>-0.0159</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1784</v>
+        <v>-0.3212</v>
       </c>
     </row>
   </sheetData>
